--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2017/DELAWARE_2017.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2017/DELAWARE_2017.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D463"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Copainalá</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -613,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -652,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>La Grandeza</t>
@@ -665,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -678,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -691,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -704,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C26">
@@ -717,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -730,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Metapa</t>
@@ -743,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -756,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -769,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -782,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C32">
@@ -795,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -808,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -821,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -834,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -847,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -878,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Dr. Belisario Domínguez</t>
@@ -891,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C40">
@@ -904,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -917,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Santa Bárbara</t>
@@ -930,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -943,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -974,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -987,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1000,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1046,7 +1261,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1062,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1075,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1088,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1114,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1127,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1140,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1153,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1166,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1179,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1192,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1205,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1218,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1249,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -1262,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1275,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1288,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1301,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -1314,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1327,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -1340,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -1353,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1368,12 +1693,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C75">
@@ -1384,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C76">
@@ -1397,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C77">
@@ -1410,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Amanalco</t>
@@ -1423,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1436,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Amecameca</t>
@@ -1449,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C81">
@@ -1462,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1475,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1488,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Calimaya</t>
@@ -1501,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Capulhuac</t>
@@ -1514,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1527,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1540,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1553,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Cocotitlán</t>
@@ -1566,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Coyotepec</t>
@@ -1579,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1592,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Cuautitlán Izcalli</t>
@@ -1605,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C93">
@@ -1618,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1631,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1644,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C96">
@@ -1657,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -1683,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Jocotitlán</t>
@@ -1696,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1709,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -1722,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -1735,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -1748,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C104">
@@ -1761,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1774,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Ocuilan</t>
@@ -1787,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Otzoloapan</t>
@@ -1800,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Otzolotepec</t>
@@ -1813,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -1826,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C110">
@@ -1839,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>San Mateo Atenco</t>
@@ -1852,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>San Simón de Guerrero</t>
+          <t>San Simón De Guerrero</t>
         </is>
       </c>
       <c r="C112">
@@ -1865,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -1878,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1891,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -1904,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Temoaya</t>
@@ -1917,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1930,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C118">
@@ -1943,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -1956,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Tepetlixpa</t>
@@ -1969,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Texcaltitlán</t>
@@ -1982,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Timilpan</t>
@@ -1995,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C123">
@@ -2008,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2021,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2034,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -2047,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Valle de Bravo</t>
+          <t>Valle De Bravo</t>
         </is>
       </c>
       <c r="C127">
@@ -2060,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Villa de Allende</t>
+          <t>Villa De Allende</t>
         </is>
       </c>
       <c r="C128">
@@ -2073,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -2086,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -2099,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -2112,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Zinacantepec</t>
@@ -2125,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Zumpahuacán</t>
@@ -2138,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2169,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2182,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C137">
@@ -2195,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2208,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -2221,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Coroneo</t>
@@ -2234,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -2247,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -2260,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -2273,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>León</t>
@@ -2286,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -2299,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2312,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2325,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2338,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -2351,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -2364,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C151">
@@ -2377,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C152">
@@ -2390,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -2403,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -2416,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2436,7 +3156,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C156">
@@ -2447,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -2460,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -2473,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -2486,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Buenavista de Cuéllar</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C160">
@@ -2499,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C161">
@@ -2512,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C162">
@@ -2525,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -2538,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -2551,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -2564,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -2577,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -2590,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Huamuxtitlán</t>
@@ -2603,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C169">
@@ -2616,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C170">
@@ -2629,9 +3419,14 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C171">
@@ -2642,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -2655,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C173">
@@ -2668,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2681,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -2694,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Pilcaya</t>
@@ -2707,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -2720,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -2733,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -2746,9 +3581,14 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C180">
@@ -2759,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C181">
@@ -2772,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -2785,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C183">
@@ -2798,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -2811,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -2824,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Tlalchapa</t>
@@ -2837,9 +3707,14 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C187">
@@ -2850,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -2863,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -2876,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2907,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -2920,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -2933,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -2946,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2959,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Lolotla</t>
@@ -2972,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C197">
@@ -2985,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Tizayuca</t>
@@ -2998,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -3011,9 +3941,14 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C200">
@@ -3024,9 +3959,14 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C201">
@@ -3037,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3057,7 +4002,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ahualulco de Mercado</t>
+          <t>Ahualulco De Mercado</t>
         </is>
       </c>
       <c r="C203">
@@ -3068,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Chimaltitán</t>
@@ -3081,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -3094,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C206">
@@ -3107,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -3120,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -3133,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C209">
@@ -3146,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Mazamitla</t>
@@ -3159,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -3172,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -3185,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C213">
@@ -3198,9 +4193,14 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>San Martín de Bolaños</t>
+          <t>San Martín De Bolaños</t>
         </is>
       </c>
       <c r="C214">
@@ -3211,9 +4211,14 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C215">
@@ -3224,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -3237,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -3250,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3281,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Angangueo</t>
@@ -3294,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -3307,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -3320,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Chavinda</t>
@@ -3333,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -3346,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -3359,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -3372,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Ixtlán</t>
@@ -3385,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -3398,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -3411,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -3424,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -3437,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -3450,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -3463,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Nuevo Urecho</t>
@@ -3476,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -3489,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -3502,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -3515,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -3528,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -3541,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -3554,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -3567,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Taretan</t>
@@ -3580,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Tarímbaro</t>
@@ -3593,9 +4733,14 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C244">
@@ -3606,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -3619,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -3632,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Tzintzuntzan</t>
@@ -3645,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -3658,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -3671,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -3684,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -3697,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -3710,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3741,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Axochiapan</t>
@@ -3754,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -3767,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -3780,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -3793,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Huitzilac</t>
@@ -3806,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Jiutepec</t>
@@ -3819,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -3832,9 +5057,14 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Jonacatepec de Leandro Valle</t>
+          <t>Jonacatepec De Leandro Valle</t>
         </is>
       </c>
       <c r="C262">
@@ -3845,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C263">
@@ -3858,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -3871,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -3884,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Tetecala</t>
@@ -3897,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C267">
@@ -3910,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -3923,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Tlayacapan</t>
@@ -3936,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Xochitepec</t>
@@ -3949,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Yecapixtla</t>
@@ -3962,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Zacatepec</t>
@@ -3975,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4006,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -4019,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -4032,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C277">
@@ -4045,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -4058,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -4071,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4102,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -4115,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4146,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Fresnillo de Trujano</t>
+          <t>Fresnillo De Trujano</t>
         </is>
       </c>
       <c r="C285">
@@ -4159,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C286">
@@ -4172,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>La Reforma</t>
@@ -4185,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Magdalena Teitipac</t>
@@ -4198,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Magdalena Tequisistlán</t>
@@ -4211,9 +5561,14 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C290">
@@ -4224,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -4237,9 +5597,14 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C292">
@@ -4250,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C293">
@@ -4263,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C294">
@@ -4276,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -4289,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -4302,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>San Sebastián Abasolo</t>
@@ -4315,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Santa Cruz Xitla</t>
@@ -4328,9 +5723,14 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Santa Inés del Monte</t>
+          <t>Santa Inés Del Monte</t>
         </is>
       </c>
       <c r="C299">
@@ -4341,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -4354,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -4367,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -4380,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -4393,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -4406,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -4419,9 +5849,14 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Santo Domingo de Morelos</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C306">
@@ -4432,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Santo Domingo Roayaga</t>
@@ -4445,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Santo Domingo Zanatepec</t>
@@ -4458,9 +5903,14 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C309">
@@ -4471,9 +5921,14 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C310">
@@ -4484,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4515,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -4528,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Ajalpan</t>
@@ -4541,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -4554,9 +6029,14 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Ayotoxco de Guerrero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C316">
@@ -4567,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Calpan</t>
@@ -4580,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -4593,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -4606,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -4619,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -4632,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Cohetzala</t>
@@ -4645,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -4658,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Cuautinchán</t>
@@ -4671,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Cuyoaco</t>
@@ -4684,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Domingo Arenas</t>
@@ -4697,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4710,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -4723,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -4736,9 +6281,14 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C330">
@@ -4749,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -4762,9 +6317,14 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Ixcamilpa de Guerrero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C332">
@@ -4775,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -4788,9 +6353,14 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C334">
@@ -4801,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Juan N. Méndez</t>
@@ -4814,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -4827,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Ocoyucan</t>
@@ -4840,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -4853,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -4866,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -4879,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -4892,9 +6497,14 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C342">
@@ -4905,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -4918,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -4931,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -4944,9 +6569,14 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C346">
@@ -4957,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Tepeyahualco</t>
@@ -4970,9 +6605,14 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C348">
@@ -4983,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -4996,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Tilapa</t>
@@ -5009,9 +6659,14 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C351">
@@ -5022,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -5035,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -5048,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -5061,9 +6731,14 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Tuzamapan de Galeana</t>
+          <t>Tuzamapan De Galeana</t>
         </is>
       </c>
       <c r="C355">
@@ -5074,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -5087,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -5100,6 +6785,11 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
           <t>Yaonáhuac</t>
@@ -5113,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -5126,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Zoquitlán</t>
@@ -5139,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5159,7 +6864,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C362">
@@ -5170,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -5183,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -5196,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5227,6 +6947,11 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5247,7 +6972,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C368">
@@ -5258,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -5271,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -5284,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -5297,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -5310,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C373">
@@ -5323,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -5336,6 +7091,11 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
           <t>San Nicolás Tolentino</t>
@@ -5349,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Santa Catarina</t>
@@ -5362,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -5375,6 +7145,11 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -5388,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -5401,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tanquián de Escobedo</t>
+          <t>Tanquián De Escobedo</t>
         </is>
       </c>
       <c r="C380">
@@ -5414,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5445,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5476,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5507,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -5520,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -5533,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -5546,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -5559,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -5572,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5603,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -5616,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -5629,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -5642,6 +7487,11 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5673,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -5686,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -5699,9 +7559,14 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C401">
@@ -5712,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -5725,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -5738,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -5751,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Totolac</t>
@@ -5764,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -5777,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -5790,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5821,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -5834,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -5847,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Apazapan</t>
@@ -5860,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -5873,9 +7793,14 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Boca del Río</t>
+          <t>Boca Del Río</t>
         </is>
       </c>
       <c r="C414">
@@ -5886,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>Carlos A. Carrillo</t>
@@ -5899,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -5912,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -5925,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -5938,9 +7883,14 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C419">
@@ -5951,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -5964,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Cotaxtla</t>
@@ -5977,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Coyutla</t>
@@ -5990,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -6003,6 +7973,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Fortín</t>
@@ -6016,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -6029,9 +8009,14 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C426">
@@ -6042,9 +8027,14 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Sureste</t>
+          <t>Ixhuatlán Del Sureste</t>
         </is>
       </c>
       <c r="C427">
@@ -6055,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Ixmatlahuacan</t>
@@ -6068,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Jalcomulco</t>
@@ -6081,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -6094,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -6107,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -6120,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -6133,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -6146,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -6159,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -6172,6 +8207,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -6185,9 +8225,14 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C438">
@@ -6198,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -6211,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Tantima</t>
@@ -6224,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Tatatila</t>
@@ -6237,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -6250,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -6263,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -6276,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Tlacotalpan</t>
@@ -6289,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -6302,6 +8387,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -6315,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -6328,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -6341,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -6354,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -6367,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -6380,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6411,6 +8531,11 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6442,6 +8567,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -6455,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -6468,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -6481,9 +8621,14 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C460">
@@ -6494,9 +8639,14 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C461">
@@ -6507,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6530,76 +8685,6 @@
       </c>
       <c r="D463">
         <v>1</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 826,856</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>Junio de 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
